--- a/assets/cm-templates/dialysis-lease-comps-template.xlsx
+++ b/assets/cm-templates/dialysis-lease-comps-template.xlsx
@@ -338,38 +338,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Subject" displayName="Subject" ref="B3:W4" headerRowCount="1">
-  <autoFilter ref="B3:W4"/>
-  <tableColumns count="22">
-    <tableColumn id="2" name="TENANT"/>
-    <tableColumn id="3" name="OPERATOR"/>
-    <tableColumn id="4" name="ADDRESS"/>
-    <tableColumn id="5" name="CITY"/>
-    <tableColumn id="6" name="STATE"/>
-    <tableColumn id="7" name="LAND"/>
-    <tableColumn id="8" name="BUILT"/>
-    <tableColumn id="9" name="RENOVATED"/>
-    <tableColumn id="10" name="RBA"/>
-    <tableColumn id="11" name="SF LEASED"/>
-    <tableColumn id="12" name="OCCUPANCY"/>
-    <tableColumn id="13" name="RENT/SF"/>
-    <tableColumn id="14" name="CURRENT RENT"/>
-    <tableColumn id="15" name="COMMENCE"/>
-    <tableColumn id="16" name="EXP"/>
-    <tableColumn id="17" name="INITIAL TERM"/>
-    <tableColumn id="18" name="TERM REM"/>
-    <tableColumn id="19" name="EXPENSES"/>
-    <tableColumn id="20" name="BUMPS"/>
-    <tableColumn id="21" name="USER/OWNER"/>
-    <tableColumn id="22" name="DISTANCE TO SUBJECT"/>
-    <tableColumn id="23" name="PATIENTS"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Comps" displayName="Comps" ref="B7:W60" headerRowCount="1" totalsRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comps" displayName="Comps" ref="B7:W60" headerRowCount="1" totalsRowCount="1">
   <autoFilter ref="B7:W60"/>
   <tableColumns count="22">
     <tableColumn id="2" name="TENANT"/>
@@ -2060,9 +2029,8 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <tableParts count="2">
+  <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/assets/cm-templates/dialysis-lease-comps-template.xlsx
+++ b/assets/cm-templates/dialysis-lease-comps-template.xlsx
@@ -345,16 +345,16 @@
     <tableColumn id="3" name="OPERATOR"/>
     <tableColumn id="4" name="ADDRESS"/>
     <tableColumn id="5" name="CITY"/>
-    <tableColumn id="6" name="STATE"/>
+    <tableColumn id="6" name="ST"/>
     <tableColumn id="7" name="LAND"/>
     <tableColumn id="8" name="BUILT"/>
-    <tableColumn id="9" name="RENOVATED"/>
+    <tableColumn id="9" name="RENO"/>
     <tableColumn id="10" name="RBA"/>
     <tableColumn id="11" name="SF LEASED"/>
     <tableColumn id="12" name="OCCUPANCY"/>
     <tableColumn id="13" name="RENT/SF"/>
     <tableColumn id="14" name="CURRENT RENT"/>
-    <tableColumn id="15" name="COMMENCE"/>
+    <tableColumn id="15" name="COMM"/>
     <tableColumn id="16" name="EXP"/>
     <tableColumn id="17" name="INITIAL TERM"/>
     <tableColumn id="18" name="TERM REM"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>RENOVATED</t>
+          <t>RENO</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>COMMENCE</t>
+          <t>COMM</t>
         </is>
       </c>
       <c r="P3" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>RENOVATED</t>
+          <t>RENO</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>COMMENCE</t>
+          <t>COMM</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
@@ -1974,7 +1974,7 @@
         <v/>
       </c>
       <c r="I60" s="35">
-        <f>IFERROR(SUBTOTAL(101,Comps[RENOVATED]),"")</f>
+        <f>IFERROR(SUBTOTAL(101,Comps[RENO]),"")</f>
         <v/>
       </c>
       <c r="J60" s="36">

--- a/assets/cm-templates/dialysis-lease-comps-template.xlsx
+++ b/assets/cm-templates/dialysis-lease-comps-template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lease Comps" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lease Comps" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Lease Comps'!$1:$7</definedName>
@@ -338,9 +338,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comps" displayName="Comps" ref="B7:W60" headerRowCount="1" totalsRowCount="1">
-  <autoFilter ref="B7:W60"/>
-  <tableColumns count="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comps" displayName="Comps" ref="B7:Z60" headerRowCount="1" totalsRowCount="1">
+  <autoFilter ref="B7:Z60"/>
+  <tableColumns count="25">
     <tableColumn id="2" name="TENANT"/>
     <tableColumn id="3" name="OPERATOR"/>
     <tableColumn id="4" name="ADDRESS"/>
@@ -358,11 +358,14 @@
     <tableColumn id="16" name="EXP"/>
     <tableColumn id="17" name="INITIAL TERM"/>
     <tableColumn id="18" name="TERM REM"/>
-    <tableColumn id="19" name="EXPENSES"/>
-    <tableColumn id="20" name="BUMPS"/>
-    <tableColumn id="21" name="USER/OWNER"/>
-    <tableColumn id="22" name="DISTANCE TO SUBJECT"/>
-    <tableColumn id="23" name="PATIENTS"/>
+    <tableColumn id="19" name="LEASE TYPE"/>
+    <tableColumn id="20" name="EXPENSES"/>
+    <tableColumn id="21" name="BUMPS"/>
+    <tableColumn id="22" name="OPTIONS"/>
+    <tableColumn id="23" name="USER/OWNER"/>
+    <tableColumn id="24" name="DISTANCE TO SUBJECT"/>
+    <tableColumn id="25" name="PATIENTS"/>
+    <tableColumn id="26" name="NOTES"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -658,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W60"/>
+  <dimension ref="A1:Z60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -680,10 +683,13 @@
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -713,6 +719,9 @@
       <c r="U1" s="2" t="n"/>
       <c r="V1" s="2" t="n"/>
       <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="B2" s="3" t="inlineStr">
@@ -741,6 +750,9 @@
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
+      <c r="X2" s="4" t="n"/>
+      <c r="Y2" s="4" t="n"/>
+      <c r="Z2" s="4" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -835,27 +847,42 @@
       </c>
       <c r="S3" s="6" t="inlineStr">
         <is>
+          <t>LEASE TYPE</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
           <t>EXPENSES</t>
         </is>
       </c>
-      <c r="T3" s="6" t="inlineStr">
+      <c r="U3" s="6" t="inlineStr">
         <is>
           <t>BUMPS</t>
         </is>
       </c>
-      <c r="U3" s="6" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>OPTIONS</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
         <is>
           <t>USER/OWNER</t>
         </is>
       </c>
-      <c r="V3" s="6" t="inlineStr">
+      <c r="X3" s="6" t="inlineStr">
         <is>
           <t>DISTANCE TO SUBJECT</t>
         </is>
       </c>
-      <c r="W3" s="6" t="inlineStr">
+      <c r="Y3" s="6" t="inlineStr">
         <is>
           <t>PATIENTS</t>
+        </is>
+      </c>
+      <c r="Z3" s="6" t="inlineStr">
+        <is>
+          <t>NOTES</t>
         </is>
       </c>
     </row>
@@ -883,8 +910,11 @@
       <c r="S4" s="9" t="n"/>
       <c r="T4" s="9" t="n"/>
       <c r="U4" s="9" t="n"/>
-      <c r="V4" s="19" t="n"/>
-      <c r="W4" s="12" t="n"/>
+      <c r="V4" s="8" t="n"/>
+      <c r="W4" s="9" t="n"/>
+      <c r="X4" s="19" t="n"/>
+      <c r="Y4" s="12" t="n"/>
+      <c r="Z4" s="8" t="n"/>
     </row>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="24" customHeight="1">
@@ -914,6 +944,9 @@
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
+      <c r="X6" s="4" t="n"/>
+      <c r="Y6" s="4" t="n"/>
+      <c r="Z6" s="4" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1008,27 +1041,42 @@
       </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
+          <t>LEASE TYPE</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
           <t>EXPENSES</t>
         </is>
       </c>
-      <c r="T7" s="6" t="inlineStr">
+      <c r="U7" s="6" t="inlineStr">
         <is>
           <t>BUMPS</t>
         </is>
       </c>
-      <c r="U7" s="6" t="inlineStr">
+      <c r="V7" s="6" t="inlineStr">
+        <is>
+          <t>OPTIONS</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
         <is>
           <t>USER/OWNER</t>
         </is>
       </c>
-      <c r="V7" s="6" t="inlineStr">
+      <c r="X7" s="6" t="inlineStr">
         <is>
           <t>DISTANCE TO SUBJECT</t>
         </is>
       </c>
-      <c r="W7" s="6" t="inlineStr">
+      <c r="Y7" s="6" t="inlineStr">
         <is>
           <t>PATIENTS</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="inlineStr">
+        <is>
+          <t>NOTES</t>
         </is>
       </c>
     </row>
@@ -1056,8 +1104,11 @@
       <c r="S8" s="9" t="n"/>
       <c r="T8" s="9" t="n"/>
       <c r="U8" s="9" t="n"/>
-      <c r="V8" s="19" t="n"/>
-      <c r="W8" s="12" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="9" t="n"/>
+      <c r="X8" s="19" t="n"/>
+      <c r="Y8" s="12" t="n"/>
+      <c r="Z8" s="8" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="20">
@@ -1084,8 +1135,11 @@
       <c r="S9" s="22" t="n"/>
       <c r="T9" s="22" t="n"/>
       <c r="U9" s="22" t="n"/>
-      <c r="V9" s="32" t="n"/>
-      <c r="W9" s="25" t="n"/>
+      <c r="V9" s="21" t="n"/>
+      <c r="W9" s="22" t="n"/>
+      <c r="X9" s="32" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="21" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="20">
@@ -1112,8 +1166,11 @@
       <c r="S10" s="9" t="n"/>
       <c r="T10" s="9" t="n"/>
       <c r="U10" s="9" t="n"/>
-      <c r="V10" s="19" t="n"/>
-      <c r="W10" s="12" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="9" t="n"/>
+      <c r="X10" s="19" t="n"/>
+      <c r="Y10" s="12" t="n"/>
+      <c r="Z10" s="8" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="20">
@@ -1140,8 +1197,11 @@
       <c r="S11" s="22" t="n"/>
       <c r="T11" s="22" t="n"/>
       <c r="U11" s="22" t="n"/>
-      <c r="V11" s="32" t="n"/>
-      <c r="W11" s="25" t="n"/>
+      <c r="V11" s="21" t="n"/>
+      <c r="W11" s="22" t="n"/>
+      <c r="X11" s="32" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="21" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="20">
@@ -1168,8 +1228,11 @@
       <c r="S12" s="9" t="n"/>
       <c r="T12" s="9" t="n"/>
       <c r="U12" s="9" t="n"/>
-      <c r="V12" s="19" t="n"/>
-      <c r="W12" s="12" t="n"/>
+      <c r="V12" s="8" t="n"/>
+      <c r="W12" s="9" t="n"/>
+      <c r="X12" s="19" t="n"/>
+      <c r="Y12" s="12" t="n"/>
+      <c r="Z12" s="8" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="20">
@@ -1196,8 +1259,11 @@
       <c r="S13" s="22" t="n"/>
       <c r="T13" s="22" t="n"/>
       <c r="U13" s="22" t="n"/>
-      <c r="V13" s="32" t="n"/>
-      <c r="W13" s="25" t="n"/>
+      <c r="V13" s="21" t="n"/>
+      <c r="W13" s="22" t="n"/>
+      <c r="X13" s="32" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="21" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="20">
@@ -1224,8 +1290,11 @@
       <c r="S14" s="9" t="n"/>
       <c r="T14" s="9" t="n"/>
       <c r="U14" s="9" t="n"/>
-      <c r="V14" s="19" t="n"/>
-      <c r="W14" s="12" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="9" t="n"/>
+      <c r="X14" s="19" t="n"/>
+      <c r="Y14" s="12" t="n"/>
+      <c r="Z14" s="8" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="20">
@@ -1252,8 +1321,11 @@
       <c r="S15" s="22" t="n"/>
       <c r="T15" s="22" t="n"/>
       <c r="U15" s="22" t="n"/>
-      <c r="V15" s="32" t="n"/>
-      <c r="W15" s="25" t="n"/>
+      <c r="V15" s="21" t="n"/>
+      <c r="W15" s="22" t="n"/>
+      <c r="X15" s="32" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="21" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="20">
@@ -1280,8 +1352,11 @@
       <c r="S16" s="9" t="n"/>
       <c r="T16" s="9" t="n"/>
       <c r="U16" s="9" t="n"/>
-      <c r="V16" s="19" t="n"/>
-      <c r="W16" s="12" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="9" t="n"/>
+      <c r="X16" s="19" t="n"/>
+      <c r="Y16" s="12" t="n"/>
+      <c r="Z16" s="8" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="20">
@@ -1308,8 +1383,11 @@
       <c r="S17" s="22" t="n"/>
       <c r="T17" s="22" t="n"/>
       <c r="U17" s="22" t="n"/>
-      <c r="V17" s="32" t="n"/>
-      <c r="W17" s="25" t="n"/>
+      <c r="V17" s="21" t="n"/>
+      <c r="W17" s="22" t="n"/>
+      <c r="X17" s="32" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="21" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="20">
@@ -1336,8 +1414,11 @@
       <c r="S18" s="9" t="n"/>
       <c r="T18" s="9" t="n"/>
       <c r="U18" s="9" t="n"/>
-      <c r="V18" s="19" t="n"/>
-      <c r="W18" s="12" t="n"/>
+      <c r="V18" s="8" t="n"/>
+      <c r="W18" s="9" t="n"/>
+      <c r="X18" s="19" t="n"/>
+      <c r="Y18" s="12" t="n"/>
+      <c r="Z18" s="8" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="20">
@@ -1364,8 +1445,11 @@
       <c r="S19" s="22" t="n"/>
       <c r="T19" s="22" t="n"/>
       <c r="U19" s="22" t="n"/>
-      <c r="V19" s="32" t="n"/>
-      <c r="W19" s="25" t="n"/>
+      <c r="V19" s="21" t="n"/>
+      <c r="W19" s="22" t="n"/>
+      <c r="X19" s="32" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="21" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="20">
@@ -1392,8 +1476,11 @@
       <c r="S20" s="9" t="n"/>
       <c r="T20" s="9" t="n"/>
       <c r="U20" s="9" t="n"/>
-      <c r="V20" s="19" t="n"/>
-      <c r="W20" s="12" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="9" t="n"/>
+      <c r="X20" s="19" t="n"/>
+      <c r="Y20" s="12" t="n"/>
+      <c r="Z20" s="8" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="20">
@@ -1420,8 +1507,11 @@
       <c r="S21" s="22" t="n"/>
       <c r="T21" s="22" t="n"/>
       <c r="U21" s="22" t="n"/>
-      <c r="V21" s="32" t="n"/>
-      <c r="W21" s="25" t="n"/>
+      <c r="V21" s="21" t="n"/>
+      <c r="W21" s="22" t="n"/>
+      <c r="X21" s="32" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="21" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="20">
@@ -1448,8 +1538,11 @@
       <c r="S22" s="9" t="n"/>
       <c r="T22" s="9" t="n"/>
       <c r="U22" s="9" t="n"/>
-      <c r="V22" s="19" t="n"/>
-      <c r="W22" s="12" t="n"/>
+      <c r="V22" s="8" t="n"/>
+      <c r="W22" s="9" t="n"/>
+      <c r="X22" s="19" t="n"/>
+      <c r="Y22" s="12" t="n"/>
+      <c r="Z22" s="8" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="20">
@@ -1476,8 +1569,11 @@
       <c r="S23" s="22" t="n"/>
       <c r="T23" s="22" t="n"/>
       <c r="U23" s="22" t="n"/>
-      <c r="V23" s="32" t="n"/>
-      <c r="W23" s="25" t="n"/>
+      <c r="V23" s="21" t="n"/>
+      <c r="W23" s="22" t="n"/>
+      <c r="X23" s="32" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="21" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="20">
@@ -1504,8 +1600,11 @@
       <c r="S24" s="9" t="n"/>
       <c r="T24" s="9" t="n"/>
       <c r="U24" s="9" t="n"/>
-      <c r="V24" s="19" t="n"/>
-      <c r="W24" s="12" t="n"/>
+      <c r="V24" s="8" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="19" t="n"/>
+      <c r="Y24" s="12" t="n"/>
+      <c r="Z24" s="8" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="20">
@@ -1532,8 +1631,11 @@
       <c r="S25" s="22" t="n"/>
       <c r="T25" s="22" t="n"/>
       <c r="U25" s="22" t="n"/>
-      <c r="V25" s="32" t="n"/>
-      <c r="W25" s="25" t="n"/>
+      <c r="V25" s="21" t="n"/>
+      <c r="W25" s="22" t="n"/>
+      <c r="X25" s="32" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="21" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="20">
@@ -1560,8 +1662,11 @@
       <c r="S26" s="9" t="n"/>
       <c r="T26" s="9" t="n"/>
       <c r="U26" s="9" t="n"/>
-      <c r="V26" s="19" t="n"/>
-      <c r="W26" s="12" t="n"/>
+      <c r="V26" s="8" t="n"/>
+      <c r="W26" s="9" t="n"/>
+      <c r="X26" s="19" t="n"/>
+      <c r="Y26" s="12" t="n"/>
+      <c r="Z26" s="8" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="20">
@@ -1588,8 +1693,11 @@
       <c r="S27" s="22" t="n"/>
       <c r="T27" s="22" t="n"/>
       <c r="U27" s="22" t="n"/>
-      <c r="V27" s="32" t="n"/>
-      <c r="W27" s="25" t="n"/>
+      <c r="V27" s="21" t="n"/>
+      <c r="W27" s="22" t="n"/>
+      <c r="X27" s="32" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="21" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="20">
@@ -1616,8 +1724,11 @@
       <c r="S28" s="9" t="n"/>
       <c r="T28" s="9" t="n"/>
       <c r="U28" s="9" t="n"/>
-      <c r="V28" s="19" t="n"/>
-      <c r="W28" s="12" t="n"/>
+      <c r="V28" s="8" t="n"/>
+      <c r="W28" s="9" t="n"/>
+      <c r="X28" s="19" t="n"/>
+      <c r="Y28" s="12" t="n"/>
+      <c r="Z28" s="8" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="20">
@@ -1644,8 +1755,11 @@
       <c r="S29" s="22" t="n"/>
       <c r="T29" s="22" t="n"/>
       <c r="U29" s="22" t="n"/>
-      <c r="V29" s="32" t="n"/>
-      <c r="W29" s="25" t="n"/>
+      <c r="V29" s="21" t="n"/>
+      <c r="W29" s="22" t="n"/>
+      <c r="X29" s="32" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="21" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="20">
@@ -1672,8 +1786,11 @@
       <c r="S30" s="9" t="n"/>
       <c r="T30" s="9" t="n"/>
       <c r="U30" s="9" t="n"/>
-      <c r="V30" s="19" t="n"/>
-      <c r="W30" s="12" t="n"/>
+      <c r="V30" s="8" t="n"/>
+      <c r="W30" s="9" t="n"/>
+      <c r="X30" s="19" t="n"/>
+      <c r="Y30" s="12" t="n"/>
+      <c r="Z30" s="8" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="20">
@@ -1700,8 +1817,11 @@
       <c r="S31" s="22" t="n"/>
       <c r="T31" s="22" t="n"/>
       <c r="U31" s="22" t="n"/>
-      <c r="V31" s="32" t="n"/>
-      <c r="W31" s="25" t="n"/>
+      <c r="V31" s="21" t="n"/>
+      <c r="W31" s="22" t="n"/>
+      <c r="X31" s="32" t="n"/>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="21" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="20">
@@ -1728,8 +1848,11 @@
       <c r="S32" s="9" t="n"/>
       <c r="T32" s="9" t="n"/>
       <c r="U32" s="9" t="n"/>
-      <c r="V32" s="19" t="n"/>
-      <c r="W32" s="12" t="n"/>
+      <c r="V32" s="8" t="n"/>
+      <c r="W32" s="9" t="n"/>
+      <c r="X32" s="19" t="n"/>
+      <c r="Y32" s="12" t="n"/>
+      <c r="Z32" s="8" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="20">
@@ -1756,8 +1879,11 @@
       <c r="S33" s="22" t="n"/>
       <c r="T33" s="22" t="n"/>
       <c r="U33" s="22" t="n"/>
-      <c r="V33" s="32" t="n"/>
-      <c r="W33" s="25" t="n"/>
+      <c r="V33" s="21" t="n"/>
+      <c r="W33" s="22" t="n"/>
+      <c r="X33" s="32" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="21" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="20">
@@ -1784,8 +1910,11 @@
       <c r="S34" s="9" t="n"/>
       <c r="T34" s="9" t="n"/>
       <c r="U34" s="9" t="n"/>
-      <c r="V34" s="19" t="n"/>
-      <c r="W34" s="12" t="n"/>
+      <c r="V34" s="8" t="n"/>
+      <c r="W34" s="9" t="n"/>
+      <c r="X34" s="19" t="n"/>
+      <c r="Y34" s="12" t="n"/>
+      <c r="Z34" s="8" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="20">
@@ -1812,8 +1941,11 @@
       <c r="S35" s="22" t="n"/>
       <c r="T35" s="22" t="n"/>
       <c r="U35" s="22" t="n"/>
-      <c r="V35" s="32" t="n"/>
-      <c r="W35" s="25" t="n"/>
+      <c r="V35" s="21" t="n"/>
+      <c r="W35" s="22" t="n"/>
+      <c r="X35" s="32" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="21" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="20">
@@ -1840,8 +1972,11 @@
       <c r="S36" s="9" t="n"/>
       <c r="T36" s="9" t="n"/>
       <c r="U36" s="9" t="n"/>
-      <c r="V36" s="19" t="n"/>
-      <c r="W36" s="12" t="n"/>
+      <c r="V36" s="8" t="n"/>
+      <c r="W36" s="9" t="n"/>
+      <c r="X36" s="19" t="n"/>
+      <c r="Y36" s="12" t="n"/>
+      <c r="Z36" s="8" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="20">
@@ -1868,8 +2003,11 @@
       <c r="S37" s="22" t="n"/>
       <c r="T37" s="22" t="n"/>
       <c r="U37" s="22" t="n"/>
-      <c r="V37" s="32" t="n"/>
-      <c r="W37" s="25" t="n"/>
+      <c r="V37" s="21" t="n"/>
+      <c r="W37" s="22" t="n"/>
+      <c r="X37" s="32" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="21" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="20">
@@ -1896,8 +2034,11 @@
       <c r="S38" s="9" t="n"/>
       <c r="T38" s="9" t="n"/>
       <c r="U38" s="9" t="n"/>
-      <c r="V38" s="19" t="n"/>
-      <c r="W38" s="12" t="n"/>
+      <c r="V38" s="8" t="n"/>
+      <c r="W38" s="9" t="n"/>
+      <c r="X38" s="19" t="n"/>
+      <c r="Y38" s="12" t="n"/>
+      <c r="Z38" s="8" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="20">
@@ -1924,8 +2065,11 @@
       <c r="S39" s="22" t="n"/>
       <c r="T39" s="22" t="n"/>
       <c r="U39" s="22" t="n"/>
-      <c r="V39" s="32" t="n"/>
-      <c r="W39" s="25" t="n"/>
+      <c r="V39" s="21" t="n"/>
+      <c r="W39" s="22" t="n"/>
+      <c r="X39" s="32" t="n"/>
+      <c r="Y39" s="25" t="n"/>
+      <c r="Z39" s="21" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="20">
@@ -1952,8 +2096,11 @@
       <c r="S40" s="9" t="n"/>
       <c r="T40" s="9" t="n"/>
       <c r="U40" s="9" t="n"/>
-      <c r="V40" s="19" t="n"/>
-      <c r="W40" s="12" t="n"/>
+      <c r="V40" s="8" t="n"/>
+      <c r="W40" s="9" t="n"/>
+      <c r="X40" s="19" t="n"/>
+      <c r="Y40" s="12" t="n"/>
+      <c r="Z40" s="8" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="B60" s="33" t="inlineStr">
@@ -2010,21 +2157,24 @@
       <c r="S60" s="40" t="n"/>
       <c r="T60" s="40" t="n"/>
       <c r="U60" s="40" t="n"/>
-      <c r="V60" s="43">
+      <c r="V60" s="40" t="n"/>
+      <c r="W60" s="40" t="n"/>
+      <c r="X60" s="43">
         <f>IFERROR(AVERAGE(Comps[DISTANCE TO SUBJECT]),"")</f>
         <v/>
       </c>
-      <c r="W60" s="36">
+      <c r="Y60" s="36">
         <f>IFERROR(AVERAGE(Comps[PATIENTS]),"")</f>
         <v/>
       </c>
+      <c r="Z60" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B2:W2"/>
     <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B6:W6"/>
-    <mergeCell ref="B1:W1"/>
+    <mergeCell ref="B1:Z1"/>
+    <mergeCell ref="B6:Z6"/>
+    <mergeCell ref="B2:Z2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/assets/cm-templates/dialysis-lease-comps-template.xlsx
+++ b/assets/cm-templates/dialysis-lease-comps-template.xlsx
@@ -35,42 +35,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Trebuchet MS"/>
+      <name val="Calibri Light"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Trebuchet MS"/>
+      <name val="Calibri Light"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
     </font>
     <font>
-      <name val="Trebuchet MS"/>
+      <name val="Calibri Light"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Open Sans"/>
+      <name val="Calibri"/>
       <color rgb="FF3D4A54"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Open Sans"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF3D4A54"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Open Sans"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF6A748C"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Open Sans"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF191919"/>
       <sz val="11"/>
